--- a/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v5_20260416.xlsx
+++ b/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v5_20260416.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF53"/>
+  <dimension ref="A1:AF52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5218,17 +5218,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor fuse boxes or new compact covered aftermarket</t>
+          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 54000-136000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5253,22 +5253,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Covered body, firm lid, strong terminals</t>
+          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Reuse original Toyota-style boxes only if terminals are tight and no heat damage.</t>
+          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5288,27 +5288,27 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Prefer compact new covered fuse boxes online; keep original-style form factor.</t>
+          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://wellshop.pk/product/6-way-fuse-block-blade-fuse-box-holder-dc-12-32v-1-709607/</t>
+          <t>Bilal Ganj inspection only</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BILAL_GANJ_ONLY</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>https://wellshop.pk/product/6-way-fuse-block-blade-fuse-box-holder-dc-12-32v-1-709607/</t>
+          <t>Bilal Ganj (in-person complete kit verification)</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>https://sehgalmotors.pk/products/fuse-60a-box-fuse-kit-for-trucks-and-cars</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>54000</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>136000</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>fuse box - compact covered ato/atc fuse block 6-way</t>
+          <t>eps kit - complete eps column kit with ecu, shafts, u-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5364,17 +5364,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
+          <t>New parts market only (no used donor plugs)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5384,37 +5384,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PKR 54000-136000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260317_235150.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BUY_IF_ENGINE_CODE_MATCH</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
+          <t>New only; no used/refurbished plugs</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260317_235150.jpg</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
+          <t>No. Glow/heat plugs should be new only.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5434,27 +5434,27 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
+          <t>Buy new only (engine code/thread/reach confirmed first).</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj inspection only</t>
+          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>BILAL_GANJ_ONLY</t>
+          <t>BUY_AFTER_ENGINE_CODE</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj (in-person complete kit verification)</t>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/q_glow%20plug/</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.daraz.pk/catalog/?q=toyota+glow+plug</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -5468,17 +5468,17 @@
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>54000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>136000</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>eps kit - complete eps column kit with ecu, shafts, u-joints, couplers, brackets, connectors</t>
+          <t>heat plugs / glow plugs - diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5510,17 +5510,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>New parts market only (no used donor plugs)</t>
+          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>images/20260317_235150.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BUY_IF_ENGINE_CODE_MATCH</t>
+          <t>MEASURE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>New only; no used/refurbished plugs</t>
+          <t>Buy only after measured fit confirmation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260317_235150.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>No. Glow/heat plugs should be new only.</t>
+          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>MEASURE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Active local front leaf spring path.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -5580,27 +5580,27 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Buy new only (engine code/thread/reach confirmed first).</t>
+          <t>Order custom measured leaf pack from LEW first; use Popular as backup if lead time/price better.</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
+          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>BUY_AFTER_ENGINE_CODE</t>
+          <t>ACTIVE_SUSPENSION_CORE_ORDER_BY_QUOTE</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/q_glow%20plug/</t>
+          <t>https://spring.com.pk/contact-us/</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=toyota+glow+plug</t>
+          <t>https://popularspringind.com/</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -5614,17 +5614,17 @@
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>heat plugs / glow plugs - diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>local front leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260324_004852.jpg;20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
+          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Active local front leaf spring path.</t>
+          <t>Active local rear leaf spring path.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>local front leaf spring pack (new, custom to measured dimensions)</t>
+          <t>local rear leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5802,17 +5802,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
+          <t>New hardware/electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5822,47 +5822,47 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260406_031010.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_THEN_BUY_ACTIVE</t>
+          <t>INSPECT_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Buy only after measured fit confirmation</t>
+          <t>Condition-based quote</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220214.jpg</t>
+          <t>20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
+          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_PLAY_FOUND</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Active local rear leaf spring path.</t>
+          <t>Steering bushing only if wear/play confirmed.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5872,29 +5872,25 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Order custom measured leaf pack from LEW first; use Popular as backup if lead time/price better.</t>
+          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE_SUSPENSION_CORE_ORDER_BY_QUOTE</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>https://spring.com.pk/contact-us/</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>https://popularspringind.com/</t>
-        </is>
-      </c>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -5906,17 +5902,17 @@
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5936,7 +5932,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>local rear leaf spring pack (new, custom to measured dimensions)</t>
+          <t>steering bushings - steering linkage bush set</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5948,17 +5944,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
+          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>3 segments</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>New hardware/electrical market (not donor car)</t>
+          <t>Electrical workshop service (rework existing wires)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5968,47 +5964,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>images/20260406_031010.jpg</t>
+          <t>images/20260411_065030.jpg</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>INSPECT_THEN_BUY_ACTIVE</t>
+          <t>WORKSHOP_TASK</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Condition-based quote</t>
+          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20260406_031010.jpg</t>
+          <t>20260411_065030.jpg;20260321_235600.jpg</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Electrical_Master</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
+          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_PLAY_FOUND</t>
+          <t>DONE_VERIFY_INSTALL</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushing only if wear/play confirmed.</t>
+          <t>Unchanged from active parts list.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -6018,34 +6014,42 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
+          <t>DONE_VERIFY_INSTALL</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>NOT_PURCHASED</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr"/>
-      <c r="V41" s="2" t="inlineStr"/>
-      <c r="W41" s="2" t="inlineStr"/>
-      <c r="X41" s="2" t="inlineStr"/>
+          <t>COMPLETED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Task completed: 25mm² main feed split into 3 segments</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Included in market work (cost not logged yet)</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>PWR-04/PWR-05/PWR-06 split done as planned. Recheck crimp quality + continuity before final install.</t>
+        </is>
+      </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>3000</t>
@@ -6066,19 +6070,14 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>planned_or_open</t>
-        </is>
-      </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>steering bushings - steering linkage bush set</t>
+          <t>wire rework - split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -6090,27 +6089,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>3 segments</t>
+          <t>10 rolls</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Electrical workshop service (rework existing wires)</t>
+          <t>New electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
+          <t>PKR 1500-4500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -6120,32 +6119,32 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP_TASK</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
+          <t>Good adhesive and heat tolerance, not brittle PVC</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260321_235600.jpg</t>
+          <t>20260411_065030.jpg</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Electrical_Master</t>
+          <t>SUB-17</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
+          <t>N/A consumable item; buy new.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>DONE_VERIFY_INSTALL</t>
+          <t>AS_LISTED</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -6160,71 +6159,66 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
+          <t>Standard consumable; online purchase is fine.</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>DONE_VERIFY_INSTALL</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t>BUY_NOW</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ubuy.com.pk/en/search/index/view/product/B0B5VQW6XK/s/3m-electrical-tape-19mm/store/store</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_ON_HAND</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>Task completed: 25mm² main feed split into 3 segments</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>Included in market work (cost not logged yet)</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>PWR-04/PWR-05/PWR-06 split done as planned. Recheck crimp quality + continuity before final install.</t>
-        </is>
-      </c>
+          <t>NOT_PURCHASED</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>7500</t>
-        </is>
-      </c>
       <c r="AB42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>wire rework - split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>electrical tape (automotive pvc, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -6236,12 +6230,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
+          <t>Cloth harness loom tape (Tesa-style)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10 rolls</t>
+          <t>5 rolls</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -6256,7 +6250,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-4500</t>
+          <t>PKR 2500-9000</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -6271,7 +6265,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Good adhesive and heat tolerance, not brittle PVC</t>
+          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -6281,7 +6275,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SUB-17</t>
+          <t>SUB-23</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -6311,7 +6305,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -6321,12 +6315,12 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>https://www.ubuy.com.pk/en/search/index/view/product/B0B5VQW6XK/s/3m-electrical-tape-19mm/store/store</t>
+          <t>https://www.daraz.pk/catalog/?q=automotive+cloth+harness+tape</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -6340,17 +6334,17 @@
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6358,7 +6352,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr">
         <is>
           <t>YES</t>
@@ -6366,7 +6359,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>electrical tape (automotive pvc, 19mm x 18-20m)</t>
+          <t>cloth harness loom tape (tesa-style)</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6378,12 +6371,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Cloth harness loom tape (Tesa-style)</t>
+          <t>Firewall grommet assortment</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5 rolls</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -6393,17 +6386,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PKR 2500-9000</t>
+          <t>PKR 2000-7000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260411_143135.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6413,17 +6406,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
+          <t>Hole ID/OD fit and thickness for firewall panels</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg</t>
+          <t>20260411_143135.jpg</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SUB-23</t>
+          <t>SUB-11</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -6453,7 +6446,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
+          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6463,12 +6456,12 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
+          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=automotive+cloth+harness+tape</t>
+          <t>https://www.ubuy.com.pk/en/product/F3KO60UI-swpeet-246pcs-sae-metric-grease-nipple-assortment-kit-hydraulic-grease-fittings-standard-with-plasti</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -6482,17 +6475,17 @@
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6500,7 +6493,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr">
         <is>
           <t>YES</t>
@@ -6508,7 +6500,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>cloth harness loom tape (tesa-style)</t>
+          <t>firewall grommet assortment</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -6520,17 +6512,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Firewall grommet assortment</t>
+          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>New electrical market (not donor car)</t>
+          <t>Toyota donor car (Bilal Ganj)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -6540,37 +6532,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PKR 2000-7000</t>
+          <t>PKR 60000-150000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_143135.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Hole ID/OD fit and thickness for firewall panels</t>
+          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>SUB-11</t>
+          <t>229-C1</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N/A consumable item; buy new.</t>
+          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -6590,29 +6582,17 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Standard consumable; online purchase is fine.</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ubuy.com.pk/en/product/F3KO60UI-swpeet-246pcs-sae-metric-grease-nipple-assortment-kit-hydraulic-grease-fittings-standard-with-plasti</t>
-        </is>
-      </c>
+          <t>KEEP_AS_ACTIVE</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -6624,17 +6604,17 @@
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>105000</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6642,7 +6622,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr">
         <is>
           <t>YES</t>
@@ -6650,7 +6629,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>firewall grommet assortment</t>
+          <t>eps donor candidate - toyota prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6662,7 +6641,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6682,7 +6661,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PKR 60000-150000</t>
+          <t>PKR 55000-140000</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6697,7 +6676,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
+          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -6707,7 +6686,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>229-C1</t>
+          <t>229-C2</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -6754,17 +6733,17 @@
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>105000</t>
+          <t>97500</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6772,7 +6751,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr">
         <is>
           <t>YES</t>
@@ -6780,7 +6758,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>eps donor candidate - toyota prius column assist set (complete kit)</t>
+          <t>eps donor candidate - toyota corolla/axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -6792,7 +6770,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -6812,7 +6790,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-140000</t>
+          <t>PKR 50000-130000</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6827,7 +6805,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
+          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6837,7 +6815,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>229-C2</t>
+          <t>229-C3</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -6884,17 +6862,17 @@
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>97500</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6902,7 +6880,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr">
         <is>
           <t>YES</t>
@@ -6910,7 +6887,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>eps donor candidate - toyota corolla/axio column assist set (complete kit)</t>
+          <t>eps donor candidate - toyota vitz/yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6922,17 +6899,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
+          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor car (Bilal Ganj)</t>
+          <t>OME/EMU supplier or suspension fabricator</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6942,47 +6919,47 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PKR 50000-130000</t>
+          <t>PKR 12000-35000</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260411_220214.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_ONLY</t>
+          <t>CONDITIONAL_LOCAL_ACTIVE</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
+          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>229-C3</t>
+          <t>SUS-10</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
+          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>BUY_ONLY_IF_INVERSION_RISK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Only needed if spring inversion tendency appears.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6992,16 +6969,24 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
+          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>KEEP_AS_ACTIVE</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr"/>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
@@ -7014,17 +6999,17 @@
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -7032,7 +7017,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr">
         <is>
           <t>YES</t>
@@ -7040,7 +7024,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>eps donor candidate - toyota vitz/yaris column assist set (complete kit)</t>
+          <t>rear anti-inversion kit - fk08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -7052,17 +7036,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
+          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 full set (front+rear)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU supplier or suspension fabricator</t>
+          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -7072,47 +7056,47 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-35000</t>
+          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220214.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL_LOCAL_ACTIVE</t>
+          <t>QUOTE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
+          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20260411_220214.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>SUS-10</t>
+          <t>SUS-11</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
+          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_INVERSION_RISK</t>
+          <t>QUOTE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Only needed if spring inversion tendency appears.</t>
+          <t>Added to active suspension quality plan.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -7122,25 +7106,29 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>ACTIVE_SUSPENSION_CORE_ORDER_NEW</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
+          <t>https://www.agriauto.com.pk/distributors-network/</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
+        </is>
+      </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -7152,17 +7140,17 @@
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7170,7 +7158,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr">
         <is>
           <t>YES</t>
@@ -7178,7 +7165,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>rear anti-inversion kit - fk08 (spring flip prevention)</t>
+          <t>shock absorbers (new genuine, pakistan high-quality path)</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -7190,67 +7177,67 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
+          <t>Split corrugated wire conduit / outer protective hosing</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1 full set (front+rear)</t>
+          <t>As purchased (exact length to confirm)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
+          <t>Local electrical market</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
+          <t>PKR 1,000-6,000</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-12067298280348876343.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_THEN_BUY_ACTIVE</t>
+          <t>BUY_NOW_ACTIVE</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
+          <t>Correct ID for loom branches, heat tolerance, abrasion resistance</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>ai-chat-attachment-12067298280348876343.png</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>SUS-11</t>
+          <t>ELEC-LOOM-01</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
+          <t>N/A new consumable.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_FIRST_THEN_BUY</t>
+          <t>PROCURED_ON_HAND</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Added to active suspension quality plan.</t>
+          <t>Added from user market purchase update.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -7260,51 +7247,55 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
-        </is>
-      </c>
+          <t>Use split conduit on exposed runs; cloth tape for cabin bundles.</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE_SUSPENSION_CORE_ORDER_NEW</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/distributors-network/</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
-        </is>
-      </c>
+          <t>PROCURED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>NOT_PURCHASED</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="inlineStr"/>
-      <c r="X50" s="2" t="inlineStr"/>
+          <t>PROCURED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Purchased (length not yet logged)</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Not logged</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>Bought during market visit.</t>
+        </is>
+      </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7312,15 +7303,14 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>shock absorbers (new genuine, pakistan high-quality path)</t>
+          <t>split corrugated wire conduit / outer protective hosing</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -7332,12 +7322,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Split corrugated wire conduit / outer protective hosing</t>
+          <t>Booster/charging cable set (MAXXIS Booster Cable 1000 AMP)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>As purchased (exact length to confirm)</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7352,12 +7342,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PKR 1,000-6,000</t>
+          <t>PKR 2,000-10,000</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-12067298280348876343.png</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-8920882528865792364.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -7367,22 +7357,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Correct ID for loom branches, heat tolerance, abrasion resistance</t>
+          <t>Clamp quality, copper content, cable gauge, insulation flexibility</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>ai-chat-attachment-12067298280348876343.png</t>
+          <t>ai-chat-attachment-8920882528865792364.png</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ELEC-LOOM-01</t>
+          <t>ELEC-CHG-01</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N/A new consumable.</t>
+          <t>Useful workshop support item.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -7402,7 +7392,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Use split conduit on exposed runs; cloth tape for cabin bundles.</t>
+          <t>Use as workshop support; not a substitute for permanent vehicle main feeds.</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr"/>
@@ -7420,7 +7410,7 @@
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>Purchased (length not yet logged)</t>
+          <t>1 set purchased</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -7440,25 +7430,24 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
       <c r="AB51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7466,7 +7455,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>split corrugated wire conduit / outer protective hosing</t>
+          <t>booster/charging cable set (maxxis booster cable 1000 amp)</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -7478,12 +7467,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Booster/charging cable set (MAXXIS Booster Cable 1000 AMP)</t>
+          <t>Battery terminal clamps / terminators (pair)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>2 terminals</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7493,17 +7482,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PKR 2,000-10,000</t>
+          <t>PKR 500-3,000</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-8920882528865792364.png</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-4151165269365336421.png</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -7513,27 +7502,27 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Clamp quality, copper content, cable gauge, insulation flexibility</t>
+          <t>Clamp fit on battery posts, material quality, corrosion resistance</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>ai-chat-attachment-8920882528865792364.png</t>
+          <t>ai-chat-attachment-4151165269365336421.png;ai-chat-attachment-14089458610305842598.png</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ELEC-CHG-01</t>
+          <t>ELEC-BAT-TERM-01</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Useful workshop support item.</t>
+          <t>New terminals are preferred if old ones are worn/oxidized.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -7548,25 +7537,25 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Use as workshop support; not a substitute for permanent vehicle main feeds.</t>
+          <t>Use anti-corrosion paste and correct clamp torque at install.</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1 set purchased</t>
+          <t>2 terminals purchased</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -7586,17 +7575,17 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7604,7 +7593,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7612,156 +7600,10 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>booster/charging cable set (maxxis booster cable 1000 amp)</t>
+          <t>battery terminal clamps / terminators (pair)</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Battery terminal clamps / terminators (pair)</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2 terminals</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Local electrical market</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>PKR 500-3,000</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-4151165269365336421.png</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>BUY_NOW_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Clamp fit on battery posts, material quality, corrosion resistance</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>ai-chat-attachment-4151165269365336421.png;ai-chat-attachment-14089458610305842598.png</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ELEC-BAT-TERM-01</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>New terminals are preferred if old ones are worn/oxidized.</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Added from user market purchase update.</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>KEPT_IN_ACTIVE</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Use anti-corrosion paste and correct clamp torque at install.</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>2 terminals purchased</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>Not logged</t>
-        </is>
-      </c>
-      <c r="X53" s="2" t="inlineStr">
-        <is>
-          <t>Bought during market visit.</t>
-        </is>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="Z53" s="2" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>battery terminal clamps / terminators (pair)</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8084,7 +7926,6 @@
           <t>82500</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8218,7 +8059,6 @@
           <t>82500</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8352,7 +8192,6 @@
           <t>42500</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8486,7 +8325,6 @@
           <t>45000</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8620,7 +8458,6 @@
           <t>44000</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8754,7 +8591,6 @@
           <t>70000</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8888,7 +8724,6 @@
           <t>2750</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>HOLD tab</t>
@@ -8922,7 +8757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -9176,32 +9011,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11100</v>
+        <v>12000</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21000</v>
+        <v>36000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16050</v>
+        <v>24000</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -9222,32 +9057,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Kit A nut - M10 nyloc/all-metal mix</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>24 (+20% spare)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 1200-2400</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12000</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>36000</v>
+        <v>2400</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24000</v>
+        <v>1800</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -9268,12 +9103,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Kit A nut - M10 nyloc/all-metal mix</t>
+          <t>Kit A nut - M12 nut</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>24 (+20% spare)</t>
+          <t>6 (+20% spare)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -9283,17 +9118,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PKR 1200-2400</t>
+          <t>PKR 500-1100</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -9314,12 +9149,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Kit A nut - M12 nut</t>
+          <t>Kit A sleeve/spacer - Sleeve for M10 mount points</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6 (+20% spare)</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -9329,17 +9164,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PKR 500-1100</t>
+          <t>PKR 1200-3200</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1100</v>
+        <v>3200</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -9360,12 +9195,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Kit A sleeve/spacer - Sleeve for M10 mount points</t>
+          <t>Kit A spring washer - M10 spring washer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20 (+20% spare)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -9375,17 +9210,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PKR 1200-3200</t>
+          <t>PKR 300-650</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3200</v>
+        <v>650</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2200</v>
+        <v>475</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -9406,12 +9241,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Kit A spring washer - M10 spring washer</t>
+          <t>Kit A spring washer - M12 spring washer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>20 (+20% spare)</t>
+          <t>6 (+20% spare)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -9421,17 +9256,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PKR 300-650</t>
+          <t>PKR 150-350</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>475</v>
+        <v>250</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -9452,12 +9287,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kit A spring washer - M12 spring washer</t>
+          <t>Kit A washer - M10 flat washer</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>6 (+20% spare)</t>
+          <t>40 (+20% spare)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -9467,17 +9302,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PKR 150-350</t>
+          <t>PKR 400-900</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -9498,12 +9333,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Kit A washer - M10 flat washer</t>
+          <t>Kit A washer - M12 flat washer</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>40 (+20% spare)</t>
+          <t>12 (+20% spare)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -9513,17 +9348,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PKR 400-900</t>
+          <t>PKR 200-500</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -9544,32 +9379,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Kit A washer - M12 flat washer</t>
+          <t>Kit B bolt - M6x1.0 class 8.8 hex bolts lengths 12/16/20/25mm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12 (+20% spare)</t>
+          <t>220 total</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PKR 200-500</t>
+          <t>PKR 6000-13000</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>200</v>
+        <v>6000</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>500</v>
+        <v>13000</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>350</v>
+        <v>9500</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -9590,12 +9425,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Kit B bolt - M6x1.0 class 8.8 hex bolts lengths 12/16/20/25mm</t>
+          <t>Kit B bolt - M8x1.25 class 8.8 bolts lengths 16/20/25/30mm</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>220 total</t>
+          <t>120 total</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -9605,17 +9440,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PKR 6000-13000</t>
+          <t>PKR 4800-10800</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>13000</v>
+        <v>10800</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>9500</v>
+        <v>7800</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -9636,12 +9471,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kit B bolt - M8x1.25 class 8.8 bolts lengths 16/20/25/30mm</t>
+          <t>Kit B nuts - M6 flange nuts</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>120 total</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9651,17 +9486,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PKR 4800-10800</t>
+          <t>PKR 1200-2800</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4800</v>
+        <v>1200</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10800</v>
+        <v>2800</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7800</v>
+        <v>2000</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -9682,12 +9517,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Kit B nuts - M6 flange nuts</t>
+          <t>Kit B nuts - M6 nyloc</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -9697,17 +9532,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PKR 1200-2800</t>
+          <t>PKR 3200-6400</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2800</v>
+        <v>6400</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2000</v>
+        <v>4800</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -9728,12 +9563,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Kit B nuts - M6 nyloc</t>
+          <t>Kit B nuts - M8 flange nuts</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -9743,17 +9578,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PKR 3200-6400</t>
+          <t>PKR 1000-2200</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6400</v>
+        <v>2200</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4800</v>
+        <v>1600</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -9774,12 +9609,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Kit B nuts - M8 flange nuts</t>
+          <t>Kit B nuts - M8 nyloc</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -9789,17 +9624,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PKR 1000-2200</t>
+          <t>PKR 2700-6300</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1000</v>
+        <v>2700</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2200</v>
+        <v>6300</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1600</v>
+        <v>4500</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -9820,12 +9655,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Kit B nuts - M8 nyloc</t>
+          <t>Kit B spring washers - M6 spring washers</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -9835,17 +9670,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PKR 2700-6300</t>
+          <t>PKR 600-1700</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2700</v>
+        <v>600</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6300</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4500</v>
+        <v>1150</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -9866,12 +9701,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Kit B spring washers - M6 spring washers</t>
+          <t>Kit B spring washers - M8 spring washers</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9881,17 +9716,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PKR 600-1700</t>
+          <t>PKR 600-1600</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -9912,12 +9747,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kit B spring washers - M8 spring washers</t>
+          <t>Kit B washers - M6 flat washers</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9927,17 +9762,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PKR 600-1600</t>
+          <t>PKR 900-2400</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1100</v>
+        <v>1650</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -9958,12 +9793,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Kit B washers - M6 flat washers</t>
+          <t>Kit B washers - M8 flat washers</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -9973,17 +9808,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PKR 900-2400</t>
+          <t>PKR 900-2500</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
         <v>900</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -10004,32 +9839,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Kit B washers - M8 flat washers</t>
+          <t>Kit C captive nut - M6 captive/clip nuts</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PKR 900-2500</t>
+          <t>PKR 1800-4200</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2500</v>
+        <v>4200</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -10050,12 +9885,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Kit C captive nut - M6 captive/clip nuts</t>
+          <t>Kit C captive nut - M8 captive/clip nuts</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10065,17 +9900,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>PKR 1800-4200</t>
+          <t>PKR 1500-3300</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4200</v>
+        <v>3300</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -10096,12 +9931,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Kit C captive nut - M8 captive/clip nuts</t>
+          <t>Kit C rivnut - M6 steel rivnuts</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10111,17 +9946,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-3300</t>
+          <t>PKR 900-2100</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>1500</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>2400</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -10142,12 +9977,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Kit C rivnut - M6 steel rivnuts</t>
+          <t>Kit C rivnut - M8 steel rivnuts</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10157,17 +9992,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>PKR 900-2100</t>
+          <t>PKR 900-2200</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
         <v>900</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -10188,12 +10023,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Kit C rivnut - M8 steel rivnuts</t>
+          <t>Kit C weld nut - M6 weld nuts</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -10203,17 +10038,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PKR 900-2200</t>
+          <t>PKR 600-1500</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1550</v>
+        <v>1050</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -10234,12 +10069,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Kit C weld nut - M6 weld nuts</t>
+          <t>Kit C weld nut - M8 weld nuts</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -10249,17 +10084,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>PKR 600-1500</t>
+          <t>PKR 700-1600</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -10280,32 +10115,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Kit C weld nut - M8 weld nuts</t>
+          <t>Kit D flange nut - M6 serrated flange nut</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PKR 700-1600</t>
+          <t>PKR 800-1800</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1150</v>
+        <v>1300</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -10326,12 +10161,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Kit D flange nut - M6 serrated flange nut</t>
+          <t>Kit D flange nut - M8 serrated flange nut</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -10341,17 +10176,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PKR 800-1800</t>
+          <t>PKR 700-1500</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -10372,12 +10207,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Kit D flange nut - M8 serrated flange nut</t>
+          <t>Kit D star washer - M10 star/serrated washer</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -10387,17 +10222,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PKR 700-1500</t>
+          <t>PKR 700-1700</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
         <v>700</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -10418,12 +10253,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Kit D star washer - M10 star/serrated washer</t>
+          <t>Kit D star washer - M6 star/serrated washer</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -10433,17 +10268,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PKR 700-1700</t>
+          <t>PKR 700-1800</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
         <v>700</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -10464,12 +10299,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Kit D star washer - M6 star/serrated washer</t>
+          <t>Kit D star washer - M8 star/serrated washer</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -10479,17 +10314,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PKR 700-1800</t>
+          <t>PKR 800-2200</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10510,32 +10345,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Kit D star washer - M8 star/serrated washer</t>
+          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>PKR 800-2200</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>800</v>
+        <v>35000</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>2200</v>
+        <v>90000</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1500</v>
+        <v>62500</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -10549,14 +10384,14 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>MEASURE_FIRST_THEN_BUY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10566,7 +10401,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10602,32 +10437,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>SUS-10</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 12000-35000</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>90000</v>
-      </c>
       <c r="G37" s="2" t="n">
-        <v>62500</v>
+        <v>23500</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -10641,39 +10476,39 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_INVERSION_RISK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
+          <t>Shims/spacers - M10/M12 shim pack thickness 1/2/3/5mm</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>Assorted full pack</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SUS-10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-35000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>35000</v>
-      </c>
       <c r="G38" s="2" t="n">
-        <v>23500</v>
+        <v>7500</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -10687,39 +10522,39 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_INVERSION_RISK</t>
+          <t>AS_LISTED</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Shims/spacers - M10/M12 shim pack thickness 1/2/3/5mm</t>
+          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Assorted full pack</t>
+          <t>1 full set (front+rear)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>SUS-11</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>12000</v>
+        <v>80000</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>7500</v>
+        <v>52500</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -10733,39 +10568,39 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>QUOTE_FIRST_THEN_BUY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1 full set (front+rear)</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SUS-11</t>
+          <t>230</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>52500</v>
+        <v>7500</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -10779,80 +10614,34 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_PLAY_FOUND</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>1 set</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>PKR 3000-12000</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>NOT_PURCHASED</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>BUY_ONLY_IF_PLAY_FOUND</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2">
         <f>SUM(E2:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="2">
+      <c r="F41" s="2">
         <f>SUM(F2:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="2">
+      <c r="G41" s="2">
         <f>SUM(G2:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J42"/>
